--- a/docs/product_order_frequency.xlsx
+++ b/docs/product_order_frequency.xlsx
@@ -426,7 +426,7 @@
     <col width="58" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -462,7 +462,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Revenue (USD)</t>
+          <t>Net sales (USD)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
